--- a/ProductionBuild/industrials.result.xlsx
+++ b/ProductionBuild/industrials.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,49 +367,131 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturnover10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>shares500</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>totalspend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyearequityproj</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyeardivproj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>totalfiveyearview</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aena SME S A</t>
+          <t>Bidvest Group Ltd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANYYY</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>0.4075</v>
+          <t>BDVSY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D2">
-        <v>1.2225</v>
+        <v>3.802909090909091</v>
       </c>
       <c r="E2">
-        <v>7.730500221252441</v>
+        <v>41.832</v>
+      </c>
+      <c r="F2">
+        <v>23.96999931335449</v>
+      </c>
+      <c r="G2">
+        <v>21.30999946594238</v>
+      </c>
+      <c r="H2">
+        <v>-2.659999847412109</v>
+      </c>
+      <c r="I2">
+        <v>39.17200015258789</v>
+      </c>
+      <c r="J2">
+        <v>3.917200015258789</v>
+      </c>
+      <c r="K2">
+        <v>24</v>
+      </c>
+      <c r="L2">
+        <v>511.4399871826172</v>
+      </c>
+      <c r="M2">
+        <v>19.58600007629395</v>
+      </c>
+      <c r="N2">
+        <v>19.01454545454546</v>
+      </c>
+      <c r="O2">
+        <v>38.6005455308394</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -423,494 +505,1023 @@
           <t>ASR</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
+      </c>
+      <c r="D3">
         <v>8.414555555555555</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>75.73099999999999</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>206.1600036621094</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>164.9299926757813</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>-41.23001098632813</v>
+      </c>
+      <c r="I3">
+        <v>34.50098901367187</v>
+      </c>
+      <c r="J3">
+        <v>3.450098901367187</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>659.719970703125</v>
+      </c>
+      <c r="M3">
+        <v>17.25049450683593</v>
+      </c>
+      <c r="N3">
+        <v>42.07277777777777</v>
+      </c>
+      <c r="O3">
+        <v>59.32327228461371</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bidvest Group Ltd</t>
+          <t>Grupo Aeroportuario del Centro Norte SAB de CV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BDVSY</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>3.802909090909091</v>
+          <t>OMAB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D4">
-        <v>41.832</v>
+        <v>3.245666666666667</v>
       </c>
       <c r="E4">
-        <v>23.96999931335449</v>
+        <v>29.211</v>
       </c>
       <c r="F4">
-        <v>21.30999946594238</v>
+        <v>53.68999862670898</v>
       </c>
       <c r="G4">
-        <v>-2.659999847412109</v>
+        <v>51.68000030517578</v>
+      </c>
+      <c r="H4">
+        <v>-2.009998321533203</v>
+      </c>
+      <c r="I4">
+        <v>27.2010016784668</v>
+      </c>
+      <c r="J4">
+        <v>2.72010016784668</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>516.8000030517578</v>
+      </c>
+      <c r="M4">
+        <v>13.6005008392334</v>
+      </c>
+      <c r="N4">
+        <v>16.22833333333333</v>
+      </c>
+      <c r="O4">
+        <v>29.82883417256673</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brenntag SE</t>
+          <t>Copa Holdings SA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNTGY</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.3357777777777778</v>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D5">
-        <v>3.022</v>
+        <v>3.2</v>
       </c>
       <c r="E5">
-        <v>18.06999969482422</v>
+        <v>28.8</v>
       </c>
       <c r="F5">
-        <v>15.76000022888184</v>
+        <v>82.66000366210938</v>
       </c>
       <c r="G5">
-        <v>-2.309999465942383</v>
+        <v>77.23000335693359</v>
+      </c>
+      <c r="H5">
+        <v>-5.430000305175781</v>
+      </c>
+      <c r="I5">
+        <v>23.36999969482422</v>
+      </c>
+      <c r="J5">
+        <v>2.336999969482422</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>540.6100234985352</v>
+      </c>
+      <c r="M5">
+        <v>11.68499984741211</v>
+      </c>
+      <c r="N5">
+        <v>16</v>
+      </c>
+      <c r="O5">
+        <v>27.68499984741211</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>China Merchants Port Holdings Co Ltd</t>
+          <t>Stanley Black &amp; Decker Inc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CMHHY</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>1.3232618</v>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D6">
-        <v>6.616309</v>
+        <v>2.632727272727273</v>
       </c>
       <c r="E6">
-        <v>16.756591796875</v>
+        <v>28.96</v>
       </c>
       <c r="F6">
-        <v>11.20510101318359</v>
+        <v>188.6199951171875</v>
       </c>
       <c r="G6">
-        <v>-5.551490783691406</v>
+        <v>178.5599975585938</v>
+      </c>
+      <c r="H6">
+        <v>-10.05999755859375</v>
+      </c>
+      <c r="I6">
+        <v>18.90000244140625</v>
+      </c>
+      <c r="J6">
+        <v>1.890000244140625</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>535.6799926757813</v>
+      </c>
+      <c r="M6">
+        <v>9.450001220703125</v>
+      </c>
+      <c r="N6">
+        <v>13.16363636363636</v>
+      </c>
+      <c r="O6">
+        <v>22.61363758433949</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Copa Holdings SA</t>
+          <t>Intertek Group plc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CPA</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>3.2</v>
+          <t>IKTSY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D7">
-        <v>28.8</v>
+        <v>1.3262</v>
       </c>
       <c r="E7">
-        <v>82.66000366210938</v>
+        <v>13.262</v>
       </c>
       <c r="F7">
-        <v>77.23000335693359</v>
+        <v>77.44000244140625</v>
       </c>
       <c r="G7">
-        <v>-5.430000305175781</v>
+        <v>79.97499847412109</v>
+      </c>
+      <c r="H7">
+        <v>2.534996032714844</v>
+      </c>
+      <c r="I7">
+        <v>15.79699603271484</v>
+      </c>
+      <c r="J7">
+        <v>1.579699603271485</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>559.8249893188477</v>
+      </c>
+      <c r="M7">
+        <v>7.898498016357422</v>
+      </c>
+      <c r="N7">
+        <v>6.631</v>
+      </c>
+      <c r="O7">
+        <v>14.52949801635742</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deutsche Post AG</t>
+          <t>Jardine Cycle &amp; Carriage Ltd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DHLGY</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.78875</v>
+          <t>JCYGY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D8">
-        <v>7.8875</v>
+        <v>1.662</v>
       </c>
       <c r="E8">
-        <v>32.04000091552734</v>
+        <v>16.62</v>
       </c>
       <c r="F8">
-        <v>24.92000007629395</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="G8">
-        <v>-7.120000839233398</v>
+        <v>29.55999946594238</v>
+      </c>
+      <c r="H8">
+        <v>-1.090000152587891</v>
+      </c>
+      <c r="I8">
+        <v>15.52999984741211</v>
+      </c>
+      <c r="J8">
+        <v>1.552999984741211</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>502.5199909210205</v>
+      </c>
+      <c r="M8">
+        <v>7.764999923706055</v>
+      </c>
+      <c r="N8">
+        <v>8.309999999999999</v>
+      </c>
+      <c r="O8">
+        <v>16.07499992370605</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daimler Truck Holding AG</t>
+          <t>Randstad NV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DTRUY</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.9376666666666666</v>
+          <t>RANJY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D9">
-        <v>2.813</v>
+        <v>1.5622</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>15.622</v>
+      </c>
+      <c r="F9">
+        <v>33.97999954223633</v>
+      </c>
+      <c r="G9">
+        <v>32.70000076293945</v>
+      </c>
+      <c r="H9">
+        <v>-1.279998779296875</v>
+      </c>
+      <c r="I9">
+        <v>14.34200122070312</v>
+      </c>
+      <c r="J9">
+        <v>1.434200122070312</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <v>523.2000122070313</v>
+      </c>
+      <c r="M9">
+        <v>7.171000610351562</v>
+      </c>
+      <c r="N9">
+        <v>7.811</v>
+      </c>
+      <c r="O9">
+        <v>14.98200061035156</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hapag-Lloyd AG</t>
+          <t>Skanska AB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HPGLY</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>12.8664</v>
+          <t>SKBSY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D10">
-        <v>64.33200000000001</v>
+        <v>0.9433</v>
       </c>
       <c r="E10">
-        <v>153.5500030517578</v>
+        <v>9.433</v>
+      </c>
+      <c r="F10">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="G10">
+        <v>26</v>
+      </c>
+      <c r="H10">
+        <v>0.1000003814697266</v>
+      </c>
+      <c r="I10">
+        <v>9.533000381469726</v>
+      </c>
+      <c r="J10">
+        <v>0.9533000381469726</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>520</v>
+      </c>
+      <c r="M10">
+        <v>4.766500190734863</v>
+      </c>
+      <c r="N10">
+        <v>4.7165</v>
+      </c>
+      <c r="O10">
+        <v>9.483000190734863</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Intertek Group plc</t>
+          <t>Qantas Airways Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IKTSY</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>1.3262</v>
+          <t>QABSY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D11">
-        <v>13.262</v>
+        <v>0.6145</v>
       </c>
       <c r="E11">
-        <v>77.44000244140625</v>
+        <v>4.3015</v>
       </c>
       <c r="F11">
-        <v>79.97499847412109</v>
+        <v>18.47999954223633</v>
       </c>
       <c r="G11">
-        <v>2.534996032714844</v>
+        <v>19.54999923706055</v>
+      </c>
+      <c r="H11">
+        <v>1.069999694824219</v>
+      </c>
+      <c r="I11">
+        <v>5.371499694824219</v>
+      </c>
+      <c r="J11">
+        <v>0.5371499694824219</v>
+      </c>
+      <c r="K11">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>508.2999801635742</v>
+      </c>
+      <c r="M11">
+        <v>2.685749847412109</v>
+      </c>
+      <c r="N11">
+        <v>3.0725</v>
+      </c>
+      <c r="O11">
+        <v>5.75824984741211</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jardine Cycle &amp; Carriage Ltd</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JCYGY</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.662</v>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D12">
-        <v>16.62</v>
+        <v>4.412727272727273</v>
       </c>
       <c r="E12">
-        <v>30.64999961853027</v>
+        <v>48.54</v>
       </c>
       <c r="F12">
-        <v>29.55999946594238</v>
+        <v>214.3399963378906</v>
       </c>
       <c r="G12">
-        <v>-1.090000152587891</v>
+        <v>168.3999938964844</v>
+      </c>
+      <c r="H12">
+        <v>-45.94000244140625</v>
+      </c>
+      <c r="I12">
+        <v>2.599997558593749</v>
+      </c>
+      <c r="J12">
+        <v>0.2599997558593749</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>505.1999816894531</v>
+      </c>
+      <c r="M12">
+        <v>1.299998779296875</v>
+      </c>
+      <c r="N12">
+        <v>22.06363636363637</v>
+      </c>
+      <c r="O12">
+        <v>23.36363514293324</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kuehne Plus Nagel International AG</t>
+          <t>China Merchants Port Holdings Co Ltd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KHNGY</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>1.5541</v>
+          <t>CMHHY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D13">
-        <v>15.541</v>
+        <v>1.3232618</v>
       </c>
       <c r="E13">
-        <v>63.2400016784668</v>
+        <v>6.616309</v>
       </c>
       <c r="F13">
-        <v>45.4900016784668</v>
+        <v>16.756591796875</v>
       </c>
       <c r="G13">
-        <v>-17.75</v>
+        <v>11.20510101318359</v>
+      </c>
+      <c r="H13">
+        <v>-5.551490783691406</v>
+      </c>
+      <c r="I13">
+        <v>1.064818216308594</v>
+      </c>
+      <c r="J13">
+        <v>0.1064818216308594</v>
+      </c>
+      <c r="K13">
+        <v>45</v>
+      </c>
+      <c r="L13">
+        <v>504.2295455932617</v>
+      </c>
+      <c r="M13">
+        <v>0.532409108154297</v>
+      </c>
+      <c r="N13">
+        <v>6.616309</v>
+      </c>
+      <c r="O13">
+        <v>7.148718108154297</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mitsui OSK Lines Ltd</t>
+          <t>Deutsche Post AG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MSLOY</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.6085</v>
+          <t>DHLGY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D14">
-        <v>1.217</v>
+        <v>0.78875</v>
       </c>
       <c r="E14">
-        <v>12.76000022888184</v>
+        <v>7.8875</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>32.04000091552734</v>
       </c>
       <c r="G14">
-        <v>-7.760000228881836</v>
+        <v>24.92000007629395</v>
+      </c>
+      <c r="H14">
+        <v>-7.120000839233398</v>
+      </c>
+      <c r="I14">
+        <v>0.7674991607666017</v>
+      </c>
+      <c r="J14">
+        <v>0.07674991607666018</v>
+      </c>
+      <c r="K14">
+        <v>21</v>
+      </c>
+      <c r="L14">
+        <v>523.3200016021729</v>
+      </c>
+      <c r="M14">
+        <v>0.3837495803833009</v>
+      </c>
+      <c r="N14">
+        <v>3.94375</v>
+      </c>
+      <c r="O14">
+        <v>4.3274995803833</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grupo Aeroportuario del Centro Norte SAB de CV</t>
+          <t>Brenntag SE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OMAB</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>3.245666666666667</v>
+          <t>BNTGY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D15">
-        <v>29.211</v>
+        <v>0.3357777777777778</v>
       </c>
       <c r="E15">
-        <v>53.68999862670898</v>
+        <v>3.022</v>
       </c>
       <c r="F15">
-        <v>51.68000030517578</v>
+        <v>18.06999969482422</v>
       </c>
       <c r="G15">
-        <v>-2.009998321533203</v>
+        <v>15.76000022888184</v>
+      </c>
+      <c r="H15">
+        <v>-2.309999465942383</v>
+      </c>
+      <c r="I15">
+        <v>0.7120005340576174</v>
+      </c>
+      <c r="J15">
+        <v>0.07120005340576174</v>
+      </c>
+      <c r="K15">
+        <v>32</v>
+      </c>
+      <c r="L15">
+        <v>504.3200073242188</v>
+      </c>
+      <c r="M15">
+        <v>0.3560002670288087</v>
+      </c>
+      <c r="N15">
+        <v>1.678888888888889</v>
+      </c>
+      <c r="O15">
+        <v>2.034889155917698</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paychex Inc.</t>
+          <t>Kuehne Plus Nagel International AG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>2.596363636363637</v>
+          <t>KHNGY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D16">
-        <v>28.56</v>
+        <v>1.5541</v>
       </c>
       <c r="E16">
-        <v>136.5</v>
+        <v>15.541</v>
       </c>
       <c r="F16">
-        <v>93.18000030517578</v>
+        <v>63.2400016784668</v>
       </c>
       <c r="G16">
-        <v>-43.31999969482422</v>
+        <v>45.4900016784668</v>
+      </c>
+      <c r="H16">
+        <v>-17.75</v>
+      </c>
+      <c r="I16">
+        <v>-2.209</v>
+      </c>
+      <c r="J16">
+        <v>-0.2209</v>
+      </c>
+      <c r="K16">
+        <v>11</v>
+      </c>
+      <c r="L16">
+        <v>500.3900184631348</v>
+      </c>
+      <c r="M16">
+        <v>-1.1045</v>
+      </c>
+      <c r="N16">
+        <v>7.7705</v>
+      </c>
+      <c r="O16">
+        <v>6.666</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Qantas Airways Ltd</t>
+          <t>Mitsui OSK Lines Ltd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QABSY</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>0.6145</v>
+          <t>MSLOY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D17">
-        <v>4.3015</v>
+        <v>0.6085</v>
       </c>
       <c r="E17">
-        <v>18.47999954223633</v>
+        <v>1.217</v>
       </c>
       <c r="F17">
-        <v>19.54999923706055</v>
+        <v>12.76000022888184</v>
       </c>
       <c r="G17">
-        <v>1.069999694824219</v>
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>-7.760000228881836</v>
+      </c>
+      <c r="I17">
+        <v>-6.543000228881835</v>
+      </c>
+      <c r="J17">
+        <v>-0.6543000228881836</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>500</v>
+      </c>
+      <c r="M17">
+        <v>-3.271500114440918</v>
+      </c>
+      <c r="N17">
+        <v>3.0425</v>
+      </c>
+      <c r="O17">
+        <v>-0.2290001144409173</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Randstad NV</t>
+          <t>Paychex Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RANJY</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>1.5622</v>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D18">
-        <v>15.622</v>
+        <v>2.596363636363637</v>
       </c>
       <c r="E18">
-        <v>33.97999954223633</v>
+        <v>28.56</v>
       </c>
       <c r="F18">
-        <v>32.70000076293945</v>
+        <v>136.5</v>
       </c>
       <c r="G18">
-        <v>-1.279998779296875</v>
+        <v>93.18000030517578</v>
+      </c>
+      <c r="H18">
+        <v>-43.31999969482422</v>
+      </c>
+      <c r="I18">
+        <v>-14.75999969482422</v>
+      </c>
+      <c r="J18">
+        <v>-1.475999969482422</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <v>559.0800018310547</v>
+      </c>
+      <c r="M18">
+        <v>-7.379999847412108</v>
+      </c>
+      <c r="N18">
+        <v>12.98181818181818</v>
+      </c>
+      <c r="O18">
+        <v>5.601818334406076</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Skanska AB</t>
+          <t>Aena SME S A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SKBSY</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>0.9433</v>
+          <t>ANYYY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D19">
-        <v>9.433</v>
+        <v>0.4075</v>
       </c>
       <c r="E19">
-        <v>25.89999961853027</v>
+        <v>1.2225</v>
       </c>
       <c r="F19">
-        <v>26</v>
-      </c>
-      <c r="G19">
-        <v>0.1000003814697266</v>
+        <v>7.730500221252441</v>
+      </c>
+      <c r="N19">
+        <v>2.0375</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker Inc</t>
+          <t>Daimler Truck Holding AG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>2.632727272727273</v>
+          <t>DTRUY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D20">
-        <v>28.96</v>
+        <v>0.9376666666666666</v>
       </c>
       <c r="E20">
-        <v>188.6199951171875</v>
+        <v>2.813</v>
       </c>
       <c r="F20">
-        <v>178.5599975585938</v>
-      </c>
-      <c r="G20">
-        <v>-10.05999755859375</v>
+        <v>18</v>
+      </c>
+      <c r="N20">
+        <v>4.688333333333333</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Hapag-Lloyd AG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>4.412727272727273</v>
+          <t>HPGLY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>industrials</t>
+        </is>
       </c>
       <c r="D21">
-        <v>48.54</v>
+        <v>12.8664</v>
       </c>
       <c r="E21">
-        <v>214.3399963378906</v>
+        <v>64.33200000000001</v>
       </c>
       <c r="F21">
-        <v>168.3999938964844</v>
-      </c>
-      <c r="G21">
-        <v>-45.94000244140625</v>
+        <v>153.5500030517578</v>
+      </c>
+      <c r="N21">
+        <v>64.33200000000001</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
   </sheetData>
